--- a/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0751</v>
+        <v>0.07935</v>
       </c>
       <c r="E2">
-        <v>0.06619999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="F2">
-        <v>0.1805</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>6500.5</v>
+        <v>9363.5</v>
       </c>
       <c r="L2">
-        <v>0.1169710078166612</v>
+        <v>0.2008205686931382</v>
       </c>
       <c r="M2">
-        <v>4835.6476</v>
+        <v>3032.6929</v>
       </c>
       <c r="N2">
-        <v>0.04044353634078086</v>
+        <v>0.03008537353588042</v>
       </c>
       <c r="O2">
-        <v>0.7438885624182755</v>
+        <v>0.3238845410370054</v>
       </c>
       <c r="P2">
-        <v>4835.6476</v>
+        <v>3032.1449</v>
       </c>
       <c r="Q2">
-        <v>0.04044353634078086</v>
+        <v>0.03007993718434688</v>
       </c>
       <c r="R2">
-        <v>0.7438885624182755</v>
+        <v>0.3238260159128531</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.5479999999999983</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0001806974916583206</v>
       </c>
       <c r="U2">
-        <v>185838.13</v>
+        <v>333696.6</v>
       </c>
       <c r="V2">
-        <v>1.554280168008471</v>
+        <v>3.310386903551386</v>
       </c>
       <c r="W2">
-        <v>0.08135280730562036</v>
+        <v>0.0580613683183346</v>
       </c>
       <c r="X2">
-        <v>0.2906419134274791</v>
+        <v>0.3026543584529029</v>
       </c>
       <c r="Y2">
-        <v>-0.2092891061218588</v>
+        <v>-0.2445929901345684</v>
       </c>
       <c r="Z2">
-        <v>0.06760440977977925</v>
+        <v>0.06101647813420037</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0591684787316214</v>
+        <v>0.09380577238385709</v>
       </c>
       <c r="AC2">
-        <v>-0.0591684787316214</v>
+        <v>-0.09380577238385709</v>
       </c>
       <c r="AD2">
-        <v>760443.2999999999</v>
+        <v>586156.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>760443.2999999999</v>
+        <v>586156.3</v>
       </c>
       <c r="AG2">
-        <v>574605.1699999999</v>
+        <v>252459.7</v>
       </c>
       <c r="AH2">
-        <v>0.8641315705174278</v>
+        <v>0.8532621733576026</v>
       </c>
       <c r="AI2">
-        <v>0.7858029691616764</v>
+        <v>0.7761570660717539</v>
       </c>
       <c r="AJ2">
-        <v>0.8277578952965406</v>
+        <v>0.7146516500756096</v>
       </c>
       <c r="AK2">
-        <v>0.7348929977413562</v>
+        <v>0.5989460188760983</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07429999999999999</v>
+        <v>0.0955</v>
       </c>
       <c r="E3">
-        <v>0.124</v>
+        <v>0.145</v>
       </c>
       <c r="F3">
-        <v>0.0726</v>
+        <v>0.222</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>425.9</v>
+        <v>386.2</v>
       </c>
       <c r="L3">
-        <v>0.463236893626278</v>
+        <v>0.4453413284132841</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2045.5</v>
+        <v>1648.9</v>
       </c>
       <c r="V3">
-        <v>0.1919467747686879</v>
+        <v>0.1629750432419076</v>
       </c>
       <c r="W3">
-        <v>0.2238280428841707</v>
+        <v>0.1691856135278398</v>
       </c>
       <c r="X3">
-        <v>0.05189627243480569</v>
+        <v>0.08343374374731866</v>
       </c>
       <c r="Y3">
-        <v>0.171931770449365</v>
+        <v>0.08575186978052118</v>
       </c>
       <c r="Z3">
-        <v>1.028871978513876</v>
+        <v>3.53382233088835</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05174956145814964</v>
+        <v>0.08257948001820314</v>
       </c>
       <c r="AC3">
-        <v>-0.05174956145814964</v>
+        <v>-0.08257948001820314</v>
       </c>
       <c r="AD3">
-        <v>112.1</v>
+        <v>495.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>112.1</v>
+        <v>495.2</v>
       </c>
       <c r="AG3">
-        <v>-1933.4</v>
+        <v>-1153.7</v>
       </c>
       <c r="AH3">
-        <v>0.0104097987686536</v>
+        <v>0.04666107588078434</v>
       </c>
       <c r="AI3">
-        <v>0.04680975446801403</v>
+        <v>0.2197373091941782</v>
       </c>
       <c r="AJ3">
-        <v>-0.2216388481291269</v>
+        <v>-0.1287065753363529</v>
       </c>
       <c r="AK3">
-        <v>-5.535070140280566</v>
+        <v>-1.907888209029271</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>illimity Bank S.p.A. (BIT:ILTY)</t>
+          <t>Credito Emiliano S.p.A. (BIT:CE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -834,6 +834,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0537</v>
+      </c>
+      <c r="E4">
+        <v>0.113</v>
+      </c>
+      <c r="F4">
+        <v>-0.0173</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -847,82 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>61.4</v>
+        <v>293.4</v>
       </c>
       <c r="L4">
-        <v>0.2306536438767844</v>
+        <v>0.219036954087346</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>99.87179999999999</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04149050724938723</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.3403946830265849</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>99.87179999999999</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04149050724938723</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.3403946830265849</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>864</v>
+        <v>6317.8</v>
       </c>
       <c r="V4">
-        <v>0.7441860465116279</v>
+        <v>2.624652070956753</v>
       </c>
       <c r="W4">
-        <v>0.09101689890305366</v>
+        <v>0.07462610641977821</v>
       </c>
       <c r="X4">
-        <v>0.08137896773005167</v>
+        <v>0.2908800063771599</v>
       </c>
       <c r="Y4">
-        <v>0.00963793117300199</v>
+        <v>-0.2162538999573817</v>
       </c>
       <c r="Z4">
-        <v>0.4040680024286581</v>
+        <v>0.06323914736916648</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0558060494171356</v>
+        <v>0.0881090916677883</v>
       </c>
       <c r="AC4">
-        <v>-0.0558060494171356</v>
+        <v>-0.0881090916677883</v>
       </c>
       <c r="AD4">
-        <v>1246</v>
+        <v>15385.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1246</v>
+        <v>15385.9</v>
       </c>
       <c r="AG4">
-        <v>382</v>
+        <v>9068.099999999999</v>
       </c>
       <c r="AH4">
-        <v>0.5176568342334856</v>
+        <v>0.8647164615298151</v>
       </c>
       <c r="AI4">
-        <v>0.5872095763231067</v>
+        <v>0.8336846325987657</v>
       </c>
       <c r="AJ4">
-        <v>0.2475696694750486</v>
+        <v>0.7902345928611265</v>
       </c>
       <c r="AK4">
-        <v>0.303680737737499</v>
+        <v>0.7471143151390319</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.051</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="E5">
-        <v>-0.0403</v>
+        <v>0.0042</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -966,85 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>24.1</v>
+        <v>25.8</v>
       </c>
       <c r="L5">
-        <v>0.228003784295175</v>
+        <v>0.2483156881616939</v>
       </c>
       <c r="M5">
-        <v>7.477200000000001</v>
+        <v>19.848</v>
       </c>
       <c r="N5">
-        <v>0.03900469483568076</v>
+        <v>0.1515114503816794</v>
       </c>
       <c r="O5">
-        <v>0.3102572614107884</v>
+        <v>0.7693023255813953</v>
       </c>
       <c r="P5">
-        <v>7.477200000000001</v>
+        <v>19.3</v>
       </c>
       <c r="Q5">
-        <v>0.03900469483568076</v>
+        <v>0.1473282442748092</v>
       </c>
       <c r="R5">
-        <v>0.3102572614107884</v>
+        <v>0.748062015503876</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.5479999999999983</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.02760983474405473</v>
       </c>
       <c r="U5">
-        <v>1.83</v>
+        <v>145.9</v>
       </c>
       <c r="V5">
-        <v>0.009546165884194054</v>
+        <v>1.113740458015267</v>
       </c>
       <c r="W5">
-        <v>0.1078782452999105</v>
+        <v>0.08869027157098661</v>
       </c>
       <c r="X5">
-        <v>0.2080932359149028</v>
+        <v>0.4746933816746555</v>
       </c>
       <c r="Y5">
-        <v>-0.1002149906149924</v>
+        <v>-0.3860031101036689</v>
       </c>
       <c r="Z5">
-        <v>0.05492535452055933</v>
+        <v>0.07795208835070187</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05849876680727712</v>
+        <v>0.08853319476458416</v>
       </c>
       <c r="AC5">
-        <v>-0.05849876680727712</v>
+        <v>-0.08853319476458416</v>
       </c>
       <c r="AD5">
-        <v>1081.3</v>
+        <v>1573.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1081.3</v>
+        <v>1573.6</v>
       </c>
       <c r="AG5">
-        <v>1079.47</v>
+        <v>1427.7</v>
       </c>
       <c r="AH5">
-        <v>0.8494108405341713</v>
+        <v>0.923149125894638</v>
       </c>
       <c r="AI5">
-        <v>0.7817379988432621</v>
+        <v>0.8642355008787346</v>
       </c>
       <c r="AJ5">
-        <v>0.8491940495763745</v>
+        <v>0.9159556040289986</v>
       </c>
       <c r="AK5">
-        <v>0.781448851502494</v>
+        <v>0.8524090990506895</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1061,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Credito Emiliano S.p.A. (BIT:CE)</t>
+          <t>Banco di Desio e della Brianza S.p.A. (BIT:BDB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1070,13 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0451</v>
+        <v>0.0873</v>
       </c>
       <c r="E6">
-        <v>0.232</v>
-      </c>
-      <c r="F6">
-        <v>-0.0161</v>
+        <v>0.317</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1091,85 +1100,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>392</v>
+        <v>62.1</v>
       </c>
       <c r="L6">
-        <v>0.2816699001221528</v>
+        <v>0.1636794939377965</v>
       </c>
       <c r="M6">
-        <v>78.97279999999999</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03520699032588828</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.2014612244897959</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>78.97279999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03520699032588828</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.2014612244897959</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>141.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="V6">
-        <v>0.06299317908251974</v>
+        <v>0.2182648401826484</v>
       </c>
       <c r="W6">
-        <v>0.1190078630195209</v>
+        <v>0.04906375918464091</v>
       </c>
       <c r="X6">
-        <v>0.2906419134274791</v>
+        <v>0.4844638654861282</v>
       </c>
       <c r="Y6">
-        <v>-0.1716340504079582</v>
+        <v>-0.4354001063014873</v>
       </c>
       <c r="Z6">
-        <v>0.08021926714969997</v>
+        <v>0.05470090399227209</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05887696876834324</v>
+        <v>0.08854571337449005</v>
       </c>
       <c r="AC6">
-        <v>-0.05887696876834324</v>
+        <v>-0.08854571337449005</v>
       </c>
       <c r="AD6">
-        <v>19326.6</v>
+        <v>5392.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>19326.6</v>
+        <v>5392.2</v>
       </c>
       <c r="AG6">
-        <v>19185.3</v>
+        <v>5296.599999999999</v>
       </c>
       <c r="AH6">
-        <v>0.8960068985660441</v>
+        <v>0.9248739322836266</v>
       </c>
       <c r="AI6">
-        <v>0.8358858358815108</v>
+        <v>0.8327850623175648</v>
       </c>
       <c r="AJ6">
-        <v>0.8953211625693006</v>
+        <v>0.9236215254769296</v>
       </c>
       <c r="AK6">
-        <v>0.8348767178130357</v>
+        <v>0.830279184236515</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1186,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banca Popolare di Sondrio S.C.p.A. (BIT:BPSO)</t>
+          <t>Banca Popolare di Sondrio S.p.A (BIT:BPSO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1195,13 +1201,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0759</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="E7">
-        <v>0.195</v>
+        <v>0.156</v>
       </c>
       <c r="F7">
-        <v>0.16</v>
+        <v>-0.00709</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,28 +1222,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>282.4</v>
+        <v>214.2</v>
       </c>
       <c r="L7">
-        <v>0.2788034356797314</v>
+        <v>0.2457831325301205</v>
       </c>
       <c r="M7">
-        <v>31.479</v>
+        <v>88.1412</v>
       </c>
       <c r="N7">
-        <v>0.01671835997663179</v>
+        <v>0.04851720151923818</v>
       </c>
       <c r="O7">
-        <v>0.1114695467422096</v>
+        <v>0.4114901960784314</v>
       </c>
       <c r="P7">
-        <v>31.479</v>
+        <v>88.1412</v>
       </c>
       <c r="Q7">
-        <v>0.01671835997663179</v>
+        <v>0.04851720151923818</v>
       </c>
       <c r="R7">
-        <v>0.1114695467422096</v>
+        <v>0.4114901960784314</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1246,55 +1252,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>5181.1</v>
+        <v>6270.5</v>
       </c>
       <c r="V7">
-        <v>2.751659673907271</v>
+        <v>3.451588044256069</v>
       </c>
       <c r="W7">
-        <v>0.08135280730562036</v>
+        <v>0.0580613683183346</v>
       </c>
       <c r="X7">
-        <v>0.2992584517679518</v>
+        <v>0.3437616586884191</v>
       </c>
       <c r="Y7">
-        <v>-0.2179056444623314</v>
+        <v>-0.2857002903700845</v>
       </c>
       <c r="Z7">
-        <v>0.07627488779782524</v>
+        <v>0.05695557269269478</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0589033777793229</v>
+        <v>0.09348773649700876</v>
       </c>
       <c r="AC7">
-        <v>-0.0589033777793229</v>
+        <v>-0.09348773649700876</v>
       </c>
       <c r="AD7">
-        <v>16807.9</v>
+        <v>14549.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>16807.9</v>
+        <v>14549.6</v>
       </c>
       <c r="AG7">
-        <v>11626.8</v>
+        <v>8279.1</v>
       </c>
       <c r="AH7">
-        <v>0.8992605987972692</v>
+        <v>0.8889975131825764</v>
       </c>
       <c r="AI7">
-        <v>0.815272381562162</v>
+        <v>0.8171270035606376</v>
       </c>
       <c r="AJ7">
-        <v>0.8606260686765805</v>
+        <v>0.8200538837932605</v>
       </c>
       <c r="AK7">
-        <v>0.7532652638125843</v>
+        <v>0.7177186549114458</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Banca Carige S.p.A. - Cassa di Risparmio di Genova e Imperia (BIT:CRG)</t>
+          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,7 +1326,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.221</v>
+        <v>0.273</v>
+      </c>
+      <c r="E8">
+        <v>-0.206</v>
+      </c>
+      <c r="F8">
+        <v>0.16</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1335,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>-265.7</v>
+        <v>643.9</v>
       </c>
       <c r="L8">
-        <v>-0.5759809234771298</v>
+        <v>0.1912612130933286</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1347,7 +1359,7 @@
         <v>-0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1356,61 +1368,61 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>299.2</v>
+        <v>23896.8</v>
       </c>
       <c r="V8">
-        <v>0.4658259380351861</v>
+        <v>4.444593237361901</v>
       </c>
       <c r="W8">
-        <v>-0.1537082031701955</v>
+        <v>0.04280111672427546</v>
       </c>
       <c r="X8">
-        <v>0.359818002399489</v>
+        <v>0.4261602993465072</v>
       </c>
       <c r="Y8">
-        <v>-0.5135262055696845</v>
+        <v>-0.3833591826222317</v>
       </c>
       <c r="Z8">
-        <v>0.04639584821024471</v>
+        <v>0.05614686977782076</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05905076946729585</v>
+        <v>0.09380577238385709</v>
       </c>
       <c r="AC8">
-        <v>-0.05905076946729585</v>
+        <v>-0.09380577238385709</v>
       </c>
       <c r="AD8">
-        <v>7135.6</v>
+        <v>56606.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>7135.6</v>
+        <v>56606.2</v>
       </c>
       <c r="AG8">
-        <v>6836.400000000001</v>
+        <v>32709.4</v>
       </c>
       <c r="AH8">
-        <v>0.9174198691163424</v>
+        <v>0.9132565808579154</v>
       </c>
       <c r="AI8">
-        <v>0.8268845240164552</v>
+        <v>0.8210817945779725</v>
       </c>
       <c r="AJ8">
-        <v>0.914116089694733</v>
+        <v>0.8588300162789476</v>
       </c>
       <c r="AK8">
-        <v>0.8206667226870581</v>
+        <v>0.7261623028048007</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1427,7 +1439,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Banco di Desio e della Brianza S.p.A. (BIT:BDB)</t>
+          <t>BPER Banca SpA (BIT:BPE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1436,10 +1448,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0553</v>
+        <v>0.217</v>
       </c>
       <c r="E9">
-        <v>0.0146</v>
+        <v>0.866</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1454,82 +1466,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>61.1</v>
+        <v>1378</v>
       </c>
       <c r="L9">
-        <v>0.1451996197718631</v>
+        <v>0.4354558382050877</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>83.43189999999998</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.02877557425674277</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.06054564586357038</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>83.43189999999998</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.02877557425674277</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.06054564586357038</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>57.3</v>
+        <v>25161.8</v>
       </c>
       <c r="V9">
-        <v>0.1365260900643317</v>
+        <v>8.67827826446851</v>
       </c>
       <c r="W9">
-        <v>0.05326011157601115</v>
+        <v>0.1750219094915728</v>
       </c>
       <c r="X9">
-        <v>0.4313851607711381</v>
+        <v>0.4874553722777222</v>
       </c>
       <c r="Y9">
-        <v>-0.3781250491951269</v>
+        <v>-0.3124334627861494</v>
       </c>
       <c r="Z9">
-        <v>0.07938574150583885</v>
+        <v>0.07527784649932441</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.0591684787316214</v>
+        <v>0.09396479740167196</v>
       </c>
       <c r="AC9">
-        <v>-0.0591684787316214</v>
+        <v>-0.09396479740167196</v>
       </c>
       <c r="AD9">
-        <v>5745.3</v>
+        <v>35959.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>5745.3</v>
+        <v>35959.6</v>
       </c>
       <c r="AG9">
-        <v>5688</v>
+        <v>10797.8</v>
       </c>
       <c r="AH9">
-        <v>0.9319221411192214</v>
+        <v>0.9253866543143158</v>
       </c>
       <c r="AI9">
-        <v>0.819469405220368</v>
+        <v>0.8203361681935979</v>
       </c>
       <c r="AJ9">
-        <v>0.9312834618596199</v>
+        <v>0.7883217007855621</v>
       </c>
       <c r="AK9">
-        <v>0.8179817938651366</v>
+        <v>0.5782449901999634</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1546,7 +1561,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A. (BIT:BMPS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1554,11 +1569,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.237</v>
-      </c>
       <c r="F10">
-        <v>0.325</v>
+        <v>-0.63</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1573,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>372.9</v>
+        <v>-430.6</v>
       </c>
       <c r="L10">
-        <v>0.09923359412422161</v>
+        <v>-0.1777869529314616</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1585,7 +1597,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1594,61 +1606,61 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>22869.7</v>
+        <v>16219.3</v>
       </c>
       <c r="V10">
-        <v>5.061683856402992</v>
+        <v>6.259861057506754</v>
       </c>
       <c r="W10">
-        <v>0.02553567393224726</v>
+        <v>-0.05943655361850732</v>
       </c>
       <c r="X10">
-        <v>0.4678366180148418</v>
+        <v>0.2222616081223339</v>
       </c>
       <c r="Y10">
-        <v>-0.4423009440825946</v>
+        <v>-0.2816981617408412</v>
       </c>
       <c r="Z10">
-        <v>0.05317345543974439</v>
+        <v>0.07210642455738803</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05921384534120759</v>
+        <v>0.0948089470201923</v>
       </c>
       <c r="AC10">
-        <v>-0.05921384534120759</v>
+        <v>-0.0948089470201923</v>
       </c>
       <c r="AD10">
-        <v>67786.3</v>
+        <v>11125.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>67786.3</v>
+        <v>11125.2</v>
       </c>
       <c r="AG10">
-        <v>44916.60000000001</v>
+        <v>-5094.099999999999</v>
       </c>
       <c r="AH10">
-        <v>0.9375114965181974</v>
+        <v>0.8110992840582669</v>
       </c>
       <c r="AI10">
-        <v>0.8183637867236498</v>
+        <v>0.6813738700115143</v>
       </c>
       <c r="AJ10">
-        <v>0.9086028465777145</v>
+        <v>2.035116455595063</v>
       </c>
       <c r="AK10">
-        <v>0.7490869186715543</v>
+        <v>-47.03693444136609</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1665,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BPER Banca SpA (BIT:BPE)</t>
+          <t>UniCredit S.p.A. (BIT:UCG)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1674,13 +1686,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0771</v>
-      </c>
-      <c r="E11">
-        <v>0.215</v>
+        <v>0.191</v>
       </c>
       <c r="F11">
-        <v>0.242</v>
+        <v>0.316</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1695,85 +1704,82 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>733.4</v>
+        <v>2504.4</v>
       </c>
       <c r="L11">
-        <v>0.2787427311770742</v>
+        <v>0.1751941238195173</v>
       </c>
       <c r="M11">
-        <v>64.91059999999999</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.02228690128755365</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.08850640850831741</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>64.91059999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02228690128755365</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.08850640850831741</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>757</v>
+        <v>137870.2</v>
       </c>
       <c r="V11">
-        <v>0.2599141630901288</v>
+        <v>5.24334931905394</v>
       </c>
       <c r="W11">
-        <v>0.1174849819783741</v>
+        <v>0.03474733123735685</v>
       </c>
       <c r="X11">
-        <v>0.3865080813720441</v>
+        <v>0.2419742313598907</v>
       </c>
       <c r="Y11">
-        <v>-0.2690230993936701</v>
+        <v>-0.2072269001225338</v>
       </c>
       <c r="Z11">
-        <v>0.07228515147435774</v>
+        <v>0.1298546754041891</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06234115690983165</v>
+        <v>0.09511785692319305</v>
       </c>
       <c r="AC11">
-        <v>-0.06234115690983165</v>
+        <v>-0.09511785692319305</v>
       </c>
       <c r="AD11">
-        <v>35158.2</v>
+        <v>128750.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>35158.2</v>
+        <v>128750.7</v>
       </c>
       <c r="AG11">
-        <v>34401.2</v>
+        <v>-9119.500000000015</v>
       </c>
       <c r="AH11">
-        <v>0.923497597890241</v>
+        <v>0.8304085910542101</v>
       </c>
       <c r="AI11">
-        <v>0.813656992230983</v>
+        <v>0.6750643339366497</v>
       </c>
       <c r="AJ11">
-        <v>0.9219455588697985</v>
+        <v>-0.5309814379206758</v>
       </c>
       <c r="AK11">
-        <v>0.8103342276535753</v>
+        <v>-0.1725432990119844</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1799,13 +1805,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.108</v>
+        <v>0.0699</v>
       </c>
       <c r="E12">
-        <v>0.06619999999999999</v>
+        <v>0.0308</v>
       </c>
       <c r="F12">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1820,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1007.6</v>
+        <v>890.3</v>
       </c>
       <c r="L12">
-        <v>0.3635445230191947</v>
+        <v>0.3617341134405981</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1853,49 +1859,49 @@
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.08480981760333987</v>
+        <v>0.07174689134411591</v>
       </c>
       <c r="X12">
-        <v>0.1548630123241312</v>
+        <v>0.2516095339167695</v>
       </c>
       <c r="Y12">
-        <v>-0.07005319472079137</v>
+        <v>-0.1798626425726536</v>
       </c>
       <c r="Z12">
-        <v>0.07328533315000542</v>
+        <v>0.05007507599155242</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06259355305600312</v>
+        <v>0.09524696361502116</v>
       </c>
       <c r="AC12">
-        <v>-0.06259355305600312</v>
+        <v>-0.09524696361502116</v>
       </c>
       <c r="AD12">
-        <v>36741.3</v>
+        <v>42276.1</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>36741.3</v>
+        <v>42276.1</v>
       </c>
       <c r="AG12">
-        <v>36741.3</v>
+        <v>42276.1</v>
       </c>
       <c r="AH12">
-        <v>0.7882217154478696</v>
+        <v>0.8384787782625942</v>
       </c>
       <c r="AI12">
-        <v>0.745793641288793</v>
+        <v>0.8004381231516088</v>
       </c>
       <c r="AJ12">
-        <v>0.7882217154478696</v>
+        <v>0.8384787782625942</v>
       </c>
       <c r="AK12">
-        <v>0.745793641288793</v>
+        <v>0.8004381231516088</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1912,7 +1918,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A. (BIT:BMPS)</t>
+          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1921,7 +1927,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0872</v>
+        <v>0.0581</v>
+      </c>
+      <c r="E13">
+        <v>-0.123</v>
+      </c>
+      <c r="F13">
+        <v>0.137</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1936,334 +1948,90 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>268</v>
+        <v>3395.8</v>
       </c>
       <c r="L13">
-        <v>0.08066943591595931</v>
+        <v>0.195662445117946</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>2741.4</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.06754312914845494</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.8072913599151893</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>2741.4</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.06754312914845494</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.8072913599151893</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>707.5</v>
+        <v>116069.8</v>
       </c>
       <c r="V13">
-        <v>0.6988344527854603</v>
+        <v>2.859749577455072</v>
       </c>
       <c r="W13">
-        <v>0.03370984377751503</v>
+        <v>0.0437395668033716</v>
       </c>
       <c r="X13">
-        <v>0.7931777519488818</v>
+        <v>0.3026543584529029</v>
       </c>
       <c r="Y13">
-        <v>-0.7594679081713668</v>
+        <v>-0.2589147916495314</v>
       </c>
       <c r="Z13">
-        <v>0.09757596192593132</v>
+        <v>0.04089992369294116</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06281131918174671</v>
+        <v>0.09576722691730868</v>
       </c>
       <c r="AC13">
-        <v>-0.06281131918174671</v>
+        <v>-0.09576722691730868</v>
       </c>
       <c r="AD13">
-        <v>27061.2</v>
+        <v>274042</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>27061.2</v>
+        <v>274042</v>
       </c>
       <c r="AG13">
-        <v>26353.7</v>
+        <v>157972.2</v>
       </c>
       <c r="AH13">
-        <v>0.9639376496067479</v>
+        <v>0.8709993408117613</v>
       </c>
       <c r="AI13">
-        <v>0.7887837936311303</v>
+        <v>0.8162104332638767</v>
       </c>
       <c r="AJ13">
-        <v>0.9630053241053712</v>
+        <v>0.7955908452676174</v>
       </c>
       <c r="AK13">
-        <v>0.7843363095238095</v>
+        <v>0.7191033842954778</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>UniCredit S.p.A. (BIT:UCG)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.0307</v>
-      </c>
-      <c r="E14">
-        <v>-0.0129</v>
-      </c>
-      <c r="F14">
-        <v>0.256</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>2086.2</v>
-      </c>
-      <c r="L14">
-        <v>0.1152870571461728</v>
-      </c>
-      <c r="M14">
-        <v>-0</v>
-      </c>
-      <c r="N14">
-        <v>-0</v>
-      </c>
-      <c r="O14">
-        <v>-0</v>
-      </c>
-      <c r="P14">
-        <v>-0</v>
-      </c>
-      <c r="Q14">
-        <v>-0</v>
-      </c>
-      <c r="R14">
-        <v>-0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>142131.4</v>
-      </c>
-      <c r="V14">
-        <v>4.16343663952194</v>
-      </c>
-      <c r="W14">
-        <v>0.02929521295269122</v>
-      </c>
-      <c r="X14">
-        <v>0.1980022623729344</v>
-      </c>
-      <c r="Y14">
-        <v>-0.1687070494202432</v>
-      </c>
-      <c r="Z14">
-        <v>0.08383456852695459</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.06332497345246536</v>
-      </c>
-      <c r="AC14">
-        <v>-0.06332497345246536</v>
-      </c>
-      <c r="AD14">
-        <v>180141.4</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>180141.4</v>
-      </c>
-      <c r="AG14">
-        <v>38010</v>
-      </c>
-      <c r="AH14">
-        <v>0.8406846388406912</v>
-      </c>
-      <c r="AI14">
-        <v>0.7127180045950052</v>
-      </c>
-      <c r="AJ14">
-        <v>0.5268337306647447</v>
-      </c>
-      <c r="AK14">
-        <v>0.3436047126547961</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.0558</v>
-      </c>
-      <c r="E15">
-        <v>-0.173</v>
-      </c>
-      <c r="F15">
-        <v>0.201</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>1051.2</v>
-      </c>
-      <c r="L15">
-        <v>0.05148600199831515</v>
-      </c>
-      <c r="M15">
-        <v>4652.808</v>
-      </c>
-      <c r="N15">
-        <v>0.09321387788137528</v>
-      </c>
-      <c r="O15">
-        <v>4.426187214611872</v>
-      </c>
-      <c r="P15">
-        <v>4652.808</v>
-      </c>
-      <c r="Q15">
-        <v>0.09321387788137528</v>
-      </c>
-      <c r="R15">
-        <v>4.426187214611872</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>10782.3</v>
-      </c>
-      <c r="V15">
-        <v>0.2160114914435224</v>
-      </c>
-      <c r="W15">
-        <v>0.01309464342882341</v>
-      </c>
-      <c r="X15">
-        <v>0.252862486576249</v>
-      </c>
-      <c r="Y15">
-        <v>-0.2397678431474256</v>
-      </c>
-      <c r="Z15">
-        <v>0.05402714905784847</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.06385707145591164</v>
-      </c>
-      <c r="AC15">
-        <v>-0.06385707145591164</v>
-      </c>
-      <c r="AD15">
-        <v>362100.1</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>362100.1</v>
-      </c>
-      <c r="AG15">
-        <v>351317.8</v>
-      </c>
-      <c r="AH15">
-        <v>0.8788506743071559</v>
-      </c>
-      <c r="AI15">
-        <v>0.8227988149518932</v>
-      </c>
-      <c r="AJ15">
-        <v>0.8755950404901688</v>
-      </c>
-      <c r="AK15">
-        <v>0.8183482408966574</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07935</v>
+        <v>0.104</v>
       </c>
       <c r="E2">
-        <v>0.113</v>
+        <v>0.226</v>
       </c>
       <c r="F2">
-        <v>0.08349999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>9363.5</v>
+        <v>23870.4</v>
       </c>
       <c r="L2">
-        <v>0.2008205686931382</v>
+        <v>0.3453237410071943</v>
       </c>
       <c r="M2">
-        <v>3032.6929</v>
+        <v>4960.3244</v>
       </c>
       <c r="N2">
-        <v>0.03008537353588042</v>
+        <v>0.03465721574033383</v>
       </c>
       <c r="O2">
-        <v>0.3238845410370054</v>
+        <v>0.2078023158388632</v>
       </c>
       <c r="P2">
-        <v>3032.1449</v>
+        <v>4960.3244</v>
       </c>
       <c r="Q2">
-        <v>0.03007993718434688</v>
+        <v>0.03465721574033383</v>
       </c>
       <c r="R2">
-        <v>0.3238260159128531</v>
+        <v>0.2078023158388632</v>
       </c>
       <c r="S2">
-        <v>0.5479999999999983</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0001806974916583206</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>333696.6</v>
+        <v>243049.9</v>
       </c>
       <c r="V2">
-        <v>3.310386903551386</v>
+        <v>1.698161680709141</v>
       </c>
       <c r="W2">
-        <v>0.0580613683183346</v>
+        <v>0.146954986760812</v>
       </c>
       <c r="X2">
-        <v>0.3026543584529029</v>
+        <v>0.1796335504330748</v>
       </c>
       <c r="Y2">
-        <v>-0.2445929901345684</v>
+        <v>-0.03267856367226277</v>
       </c>
       <c r="Z2">
-        <v>0.06101647813420037</v>
+        <v>0.1659565217234729</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09380577238385709</v>
+        <v>0.0788301971896169</v>
       </c>
       <c r="AC2">
-        <v>-0.09380577238385709</v>
+        <v>-0.0788301971896169</v>
       </c>
       <c r="AD2">
-        <v>586156.3</v>
+        <v>540294.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>586156.3</v>
+        <v>540294.4</v>
       </c>
       <c r="AG2">
-        <v>252459.7</v>
+        <v>297244.5</v>
       </c>
       <c r="AH2">
-        <v>0.8532621733576026</v>
+        <v>0.7905748107641616</v>
       </c>
       <c r="AI2">
-        <v>0.7761570660717539</v>
+        <v>0.7382114820879728</v>
       </c>
       <c r="AJ2">
-        <v>0.7146516500756096</v>
+        <v>0.6749883847620796</v>
       </c>
       <c r="AK2">
-        <v>0.5989460188760983</v>
+        <v>0.6080527101957957</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0955</v>
+        <v>0.14</v>
       </c>
       <c r="E3">
-        <v>0.145</v>
+        <v>0.192</v>
       </c>
       <c r="F3">
-        <v>0.222</v>
+        <v>0.124</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>386.2</v>
+        <v>614.2</v>
       </c>
       <c r="L3">
-        <v>0.4453413284132841</v>
+        <v>0.4951628506933247</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1648.9</v>
+        <v>1902.9</v>
       </c>
       <c r="V3">
-        <v>0.1629750432419076</v>
+        <v>0.2075611644978676</v>
       </c>
       <c r="W3">
-        <v>0.1691856135278398</v>
+        <v>0.349294813466788</v>
       </c>
       <c r="X3">
-        <v>0.08343374374731866</v>
+        <v>0.07171592818007219</v>
       </c>
       <c r="Y3">
-        <v>0.08575186978052118</v>
+        <v>0.2775788852867158</v>
       </c>
       <c r="Z3">
-        <v>3.53382233088835</v>
+        <v>2.400154798761611</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08257948001820314</v>
+        <v>0.07063199552625604</v>
       </c>
       <c r="AC3">
-        <v>-0.08257948001820314</v>
+        <v>-0.07063199552625604</v>
       </c>
       <c r="AD3">
-        <v>495.2</v>
+        <v>845.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>495.2</v>
+        <v>845.3</v>
       </c>
       <c r="AG3">
-        <v>-1153.7</v>
+        <v>-1057.6</v>
       </c>
       <c r="AH3">
-        <v>0.04666107588078434</v>
+        <v>0.08441856749091201</v>
       </c>
       <c r="AI3">
-        <v>0.2197373091941782</v>
+        <v>0.2797709671013437</v>
       </c>
       <c r="AJ3">
-        <v>-0.1287065753363529</v>
+        <v>-0.1304020813040208</v>
       </c>
       <c r="AK3">
-        <v>-1.907888209029271</v>
+        <v>-0.9455520786767996</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0537</v>
+        <v>0.108</v>
       </c>
       <c r="E4">
-        <v>0.113</v>
+        <v>0.226</v>
       </c>
       <c r="F4">
-        <v>-0.0173</v>
+        <v>0.111</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>293.4</v>
+        <v>560.9</v>
       </c>
       <c r="L4">
-        <v>0.219036954087346</v>
+        <v>0.2999625648430397</v>
       </c>
       <c r="M4">
-        <v>99.87179999999999</v>
+        <v>118.6949</v>
       </c>
       <c r="N4">
-        <v>0.04149050724938723</v>
+        <v>0.03927043837882548</v>
       </c>
       <c r="O4">
-        <v>0.3403946830265849</v>
+        <v>0.2116150829024782</v>
       </c>
       <c r="P4">
-        <v>99.87179999999999</v>
+        <v>118.6949</v>
       </c>
       <c r="Q4">
-        <v>0.04149050724938723</v>
+        <v>0.03927043837882548</v>
       </c>
       <c r="R4">
-        <v>0.3403946830265849</v>
+        <v>0.2116150829024782</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6317.8</v>
+        <v>6091.3</v>
       </c>
       <c r="V4">
-        <v>2.624652070956753</v>
+        <v>2.015318444995864</v>
       </c>
       <c r="W4">
-        <v>0.07462610641977821</v>
+        <v>0.1827869386690999</v>
       </c>
       <c r="X4">
-        <v>0.2908800063771599</v>
+        <v>0.1589650593724325</v>
       </c>
       <c r="Y4">
-        <v>-0.2162538999573817</v>
+        <v>0.02382187929666738</v>
       </c>
       <c r="Z4">
-        <v>0.06323914736916648</v>
+        <v>0.1577841532360139</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0881090916677883</v>
+        <v>0.07451323648074738</v>
       </c>
       <c r="AC4">
-        <v>-0.0881090916677883</v>
+        <v>-0.07451323648074738</v>
       </c>
       <c r="AD4">
-        <v>15385.9</v>
+        <v>11559</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15385.9</v>
+        <v>11559</v>
       </c>
       <c r="AG4">
-        <v>9068.099999999999</v>
+        <v>5467.7</v>
       </c>
       <c r="AH4">
-        <v>0.8647164615298151</v>
+        <v>0.7927167986832631</v>
       </c>
       <c r="AI4">
-        <v>0.8336846325987657</v>
+        <v>0.7458092989044172</v>
       </c>
       <c r="AJ4">
-        <v>0.7902345928611265</v>
+        <v>0.6440013191679819</v>
       </c>
       <c r="AK4">
-        <v>0.7471143151390319</v>
+        <v>0.5812188406875511</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banca Sistema S.p.A. (BIT:BST)</t>
+          <t>Banca Popolare di Sondrio S.p.A (BIT:BPSO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +960,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.06519999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="E5">
-        <v>0.0042</v>
+        <v>0.291</v>
+      </c>
+      <c r="F5">
+        <v>0.135</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,85 +981,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>25.8</v>
+        <v>474.8</v>
       </c>
       <c r="L5">
-        <v>0.2483156881616939</v>
+        <v>0.3644458090267117</v>
       </c>
       <c r="M5">
-        <v>19.848</v>
+        <v>133.1112</v>
       </c>
       <c r="N5">
-        <v>0.1515114503816794</v>
+        <v>0.04569714030691063</v>
       </c>
       <c r="O5">
-        <v>0.7693023255813953</v>
+        <v>0.280352148272957</v>
       </c>
       <c r="P5">
-        <v>19.3</v>
+        <v>133.1112</v>
       </c>
       <c r="Q5">
-        <v>0.1473282442748092</v>
+        <v>0.04569714030691063</v>
       </c>
       <c r="R5">
-        <v>0.748062015503876</v>
+        <v>0.280352148272957</v>
       </c>
       <c r="S5">
-        <v>0.5479999999999983</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.02760983474405473</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>145.9</v>
+        <v>3867</v>
       </c>
       <c r="V5">
-        <v>1.113740458015267</v>
+        <v>1.327542998386488</v>
       </c>
       <c r="W5">
-        <v>0.08869027157098661</v>
+        <v>0.14581413918064</v>
       </c>
       <c r="X5">
-        <v>0.4746933816746555</v>
+        <v>0.1884324154705405</v>
       </c>
       <c r="Y5">
-        <v>-0.3860031101036689</v>
+        <v>-0.04261827628990053</v>
       </c>
       <c r="Z5">
-        <v>0.07795208835070187</v>
+        <v>0.1131138431617698</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08853319476458416</v>
+        <v>0.07478151524743974</v>
       </c>
       <c r="AC5">
-        <v>-0.08853319476458416</v>
+        <v>-0.07478151524743974</v>
       </c>
       <c r="AD5">
-        <v>1573.6</v>
+        <v>14811.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1573.6</v>
+        <v>14811.5</v>
       </c>
       <c r="AG5">
-        <v>1427.7</v>
+        <v>10944.5</v>
       </c>
       <c r="AH5">
-        <v>0.923149125894638</v>
+        <v>0.8356559319356367</v>
       </c>
       <c r="AI5">
-        <v>0.8642355008787346</v>
+        <v>0.7929195865029952</v>
       </c>
       <c r="AJ5">
-        <v>0.9159556040289986</v>
+        <v>0.7897946223678324</v>
       </c>
       <c r="AK5">
-        <v>0.8524090990506895</v>
+        <v>0.7388592221539625</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,10 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0873</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E6">
-        <v>0.317</v>
+        <v>0.434</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>62.1</v>
+        <v>257.4</v>
       </c>
       <c r="L6">
-        <v>0.1636794939377965</v>
+        <v>0.4941447494720675</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1127,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>95.59999999999999</v>
+        <v>2715.3</v>
       </c>
       <c r="V6">
-        <v>0.2182648401826484</v>
+        <v>5.022752497225305</v>
       </c>
       <c r="W6">
-        <v>0.04906375918464091</v>
+        <v>0.2377389858686617</v>
       </c>
       <c r="X6">
-        <v>0.4844638654861282</v>
+        <v>0.3153746443777281</v>
       </c>
       <c r="Y6">
-        <v>-0.4354001063014873</v>
+        <v>-0.0776356585090664</v>
       </c>
       <c r="Z6">
-        <v>0.05470090399227209</v>
+        <v>0.08184717879421147</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08854571337449005</v>
+        <v>0.07526572195836997</v>
       </c>
       <c r="AC6">
-        <v>-0.08854571337449005</v>
+        <v>-0.07526572195836997</v>
       </c>
       <c r="AD6">
-        <v>5392.2</v>
+        <v>5684.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>5392.2</v>
+        <v>5684.3</v>
       </c>
       <c r="AG6">
-        <v>5296.599999999999</v>
+        <v>2969</v>
       </c>
       <c r="AH6">
-        <v>0.9248739322836266</v>
+        <v>0.9131552314093399</v>
       </c>
       <c r="AI6">
-        <v>0.8327850623175648</v>
+        <v>0.8019044931932002</v>
       </c>
       <c r="AJ6">
-        <v>0.9236215254769296</v>
+        <v>0.8459653521768863</v>
       </c>
       <c r="AK6">
-        <v>0.830279184236515</v>
+        <v>0.6789078935333395</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banca Popolare di Sondrio S.p.A (BIT:BPSO)</t>
+          <t>Banca Sistema S.p.A. (BIT:BST)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,13 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.07139999999999999</v>
+        <v>0.0309</v>
       </c>
       <c r="E7">
-        <v>0.156</v>
-      </c>
-      <c r="F7">
-        <v>-0.00709</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,28 +1222,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>214.2</v>
+        <v>16.5</v>
       </c>
       <c r="L7">
-        <v>0.2457831325301205</v>
+        <v>0.1722338204592902</v>
       </c>
       <c r="M7">
-        <v>88.1412</v>
+        <v>5.5407</v>
       </c>
       <c r="N7">
-        <v>0.04851720151923818</v>
+        <v>0.05207424812030075</v>
       </c>
       <c r="O7">
-        <v>0.4114901960784314</v>
+        <v>0.3358</v>
       </c>
       <c r="P7">
-        <v>88.1412</v>
+        <v>5.5407</v>
       </c>
       <c r="Q7">
-        <v>0.04851720151923818</v>
+        <v>0.05207424812030075</v>
       </c>
       <c r="R7">
-        <v>0.4114901960784314</v>
+        <v>0.3358</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1252,55 +1252,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>6270.5</v>
+        <v>164</v>
       </c>
       <c r="V7">
-        <v>3.451588044256069</v>
+        <v>1.541353383458647</v>
       </c>
       <c r="W7">
-        <v>0.0580613683183346</v>
+        <v>0.06947368421052631</v>
       </c>
       <c r="X7">
-        <v>0.3437616586884191</v>
+        <v>0.3870081024947167</v>
       </c>
       <c r="Y7">
-        <v>-0.2857002903700845</v>
+        <v>-0.3175344182841904</v>
       </c>
       <c r="Z7">
-        <v>0.05695557269269478</v>
+        <v>0.05864707682889501</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09348773649700876</v>
+        <v>0.07537976279662342</v>
       </c>
       <c r="AC7">
-        <v>-0.09348773649700876</v>
+        <v>-0.07537976279662342</v>
       </c>
       <c r="AD7">
-        <v>14549.6</v>
+        <v>1444.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>14549.6</v>
+        <v>1444.8</v>
       </c>
       <c r="AG7">
-        <v>8279.1</v>
+        <v>1280.8</v>
       </c>
       <c r="AH7">
-        <v>0.8889975131825764</v>
+        <v>0.9314079422382671</v>
       </c>
       <c r="AI7">
-        <v>0.8171270035606376</v>
+        <v>0.83664369679773</v>
       </c>
       <c r="AJ7">
-        <v>0.8200538837932605</v>
+        <v>0.9232987312572087</v>
       </c>
       <c r="AK7">
-        <v>0.7177186549114458</v>
+        <v>0.8195022074348965</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
+          <t>UniCredit S.p.A. (BIT:UCG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.273</v>
+        <v>0.073</v>
       </c>
       <c r="E8">
-        <v>-0.206</v>
+        <v>0.253</v>
       </c>
       <c r="F8">
-        <v>0.16</v>
+        <v>0.295</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>643.9</v>
+        <v>9695.200000000001</v>
       </c>
       <c r="L8">
-        <v>0.1912612130933286</v>
+        <v>0.4082189473684211</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1374,55 +1374,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>23896.8</v>
+        <v>92506.39999999999</v>
       </c>
       <c r="V8">
-        <v>4.444593237361901</v>
+        <v>1.980246004461132</v>
       </c>
       <c r="W8">
-        <v>0.04280111672427546</v>
+        <v>0.1569391745768638</v>
       </c>
       <c r="X8">
-        <v>0.4261602993465072</v>
+        <v>0.1328571873788326</v>
       </c>
       <c r="Y8">
-        <v>-0.3833591826222317</v>
+        <v>0.02408198719803126</v>
       </c>
       <c r="Z8">
-        <v>0.05614686977782076</v>
+        <v>0.4510295818433532</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.09380577238385709</v>
+        <v>0.0788301971896169</v>
       </c>
       <c r="AC8">
-        <v>-0.09380577238385709</v>
+        <v>-0.0788301971896169</v>
       </c>
       <c r="AD8">
-        <v>56606.2</v>
+        <v>126481.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>56606.2</v>
+        <v>126481.8</v>
       </c>
       <c r="AG8">
-        <v>32709.4</v>
+        <v>33975.40000000001</v>
       </c>
       <c r="AH8">
-        <v>0.9132565808579154</v>
+        <v>0.730279613202122</v>
       </c>
       <c r="AI8">
-        <v>0.8210817945779725</v>
+        <v>0.6551536413913632</v>
       </c>
       <c r="AJ8">
-        <v>0.8588300162789476</v>
+        <v>0.4210608501673071</v>
       </c>
       <c r="AK8">
-        <v>0.7261623028048007</v>
+        <v>0.3378945662021894</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,10 +1448,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.217</v>
+        <v>0.21</v>
       </c>
       <c r="E9">
-        <v>0.866</v>
+        <v>0.226</v>
+      </c>
+      <c r="F9">
+        <v>0.4370000000000001</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1466,28 +1469,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1378</v>
+        <v>1132.2</v>
       </c>
       <c r="L9">
-        <v>0.4354558382050877</v>
+        <v>0.2229969274403215</v>
       </c>
       <c r="M9">
-        <v>83.43189999999998</v>
+        <v>179.7304</v>
       </c>
       <c r="N9">
-        <v>0.02877557425674277</v>
+        <v>0.03797067646934551</v>
       </c>
       <c r="O9">
-        <v>0.06054564586357038</v>
+        <v>0.1587443914502738</v>
       </c>
       <c r="P9">
-        <v>83.43189999999998</v>
+        <v>179.7304</v>
       </c>
       <c r="Q9">
-        <v>0.02877557425674277</v>
+        <v>0.03797067646934551</v>
       </c>
       <c r="R9">
-        <v>0.06054564586357038</v>
+        <v>0.1587443914502738</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1496,55 +1499,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>25161.8</v>
+        <v>12267.7</v>
       </c>
       <c r="V9">
-        <v>8.67827826446851</v>
+        <v>2.59173110237884</v>
       </c>
       <c r="W9">
-        <v>0.1750219094915728</v>
+        <v>0.146954986760812</v>
       </c>
       <c r="X9">
-        <v>0.4874553722777222</v>
+        <v>0.2281410648259944</v>
       </c>
       <c r="Y9">
-        <v>-0.3124334627861494</v>
+        <v>-0.08118607806518241</v>
       </c>
       <c r="Z9">
-        <v>0.07527784649932441</v>
+        <v>0.2774153361964397</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.09396479740167196</v>
+        <v>0.07885520450028874</v>
       </c>
       <c r="AC9">
-        <v>-0.09396479740167196</v>
+        <v>-0.07885520450028874</v>
       </c>
       <c r="AD9">
-        <v>35959.6</v>
+        <v>32108.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>35959.6</v>
+        <v>32108.3</v>
       </c>
       <c r="AG9">
-        <v>10797.8</v>
+        <v>19840.6</v>
       </c>
       <c r="AH9">
-        <v>0.9253866543143158</v>
+        <v>0.871520586726454</v>
       </c>
       <c r="AI9">
-        <v>0.8203361681935979</v>
+        <v>0.7701512800155429</v>
       </c>
       <c r="AJ9">
-        <v>0.7883217007855621</v>
+        <v>0.8073817856270855</v>
       </c>
       <c r="AK9">
-        <v>0.5782449901999634</v>
+        <v>0.6743182250740912</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1561,7 +1564,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A. (BIT:BMPS)</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A. (BIT:MB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1569,8 +1572,14 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.104</v>
+      </c>
+      <c r="E10">
+        <v>0.0665</v>
+      </c>
       <c r="F10">
-        <v>-0.63</v>
+        <v>0.139</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1585,10 +1594,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-430.6</v>
+        <v>1180.7</v>
       </c>
       <c r="L10">
-        <v>-0.1777869529314616</v>
+        <v>0.3674644424387663</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1597,7 +1606,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1606,61 +1615,61 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>16219.3</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>6.259861057506754</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>-0.05943655361850732</v>
+        <v>0.1130884536181217</v>
       </c>
       <c r="X10">
-        <v>0.2222616081223339</v>
+        <v>0.1470837726097598</v>
       </c>
       <c r="Y10">
-        <v>-0.2816981617408412</v>
+        <v>-0.03399531899163806</v>
       </c>
       <c r="Z10">
-        <v>0.07210642455738803</v>
+        <v>0.06098352566049195</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0948089470201923</v>
+        <v>0.07931291944586655</v>
       </c>
       <c r="AC10">
-        <v>-0.0948089470201923</v>
+        <v>-0.07931291944586655</v>
       </c>
       <c r="AD10">
-        <v>11125.2</v>
+        <v>34560.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>11125.2</v>
+        <v>34560.3</v>
       </c>
       <c r="AG10">
-        <v>-5094.099999999999</v>
+        <v>34560.3</v>
       </c>
       <c r="AH10">
-        <v>0.8110992840582669</v>
+        <v>0.7683088681548076</v>
       </c>
       <c r="AI10">
-        <v>0.6813738700115143</v>
+        <v>0.7489305728315657</v>
       </c>
       <c r="AJ10">
-        <v>2.035116455595063</v>
+        <v>0.7683088681548076</v>
       </c>
       <c r="AK10">
-        <v>-47.03693444136609</v>
+        <v>0.7489305728315657</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1677,7 +1686,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UniCredit S.p.A. (BIT:UCG)</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A. (BIT:BMPS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1686,10 +1695,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.191</v>
+        <v>0.11</v>
       </c>
       <c r="F11">
-        <v>0.316</v>
+        <v>0.12</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1704,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>2504.4</v>
+        <v>1120.1</v>
       </c>
       <c r="L11">
-        <v>0.1751941238195173</v>
+        <v>0.3334127102247358</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1731,55 +1740,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>137870.2</v>
+        <v>14304.1</v>
       </c>
       <c r="V11">
-        <v>5.24334931905394</v>
+        <v>3.372653965858719</v>
       </c>
       <c r="W11">
-        <v>0.03474733123735685</v>
+        <v>0.2153582895925862</v>
       </c>
       <c r="X11">
-        <v>0.2419742313598907</v>
+        <v>0.1758194379058632</v>
       </c>
       <c r="Y11">
-        <v>-0.2072269001225338</v>
+        <v>0.03953885168672294</v>
       </c>
       <c r="Z11">
-        <v>0.1298546754041891</v>
+        <v>33.84886649873993</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.09511785692319305</v>
+        <v>0.07996482010825361</v>
       </c>
       <c r="AC11">
-        <v>-0.09511785692319305</v>
+        <v>-0.07996482010825361</v>
       </c>
       <c r="AD11">
-        <v>128750.7</v>
+        <v>19277.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>128750.7</v>
+        <v>19277.4</v>
       </c>
       <c r="AG11">
-        <v>-9119.500000000015</v>
+        <v>4973.300000000001</v>
       </c>
       <c r="AH11">
-        <v>0.8304085910542101</v>
+        <v>0.819666136589763</v>
       </c>
       <c r="AI11">
-        <v>0.6750643339366497</v>
+        <v>0.674039678599151</v>
       </c>
       <c r="AJ11">
-        <v>-0.5309814379206758</v>
+        <v>0.5397254327418743</v>
       </c>
       <c r="AK11">
-        <v>-0.1725432990119844</v>
+        <v>0.3478878264093399</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1796,7 +1805,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A. (BIT:MB)</t>
+          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1805,13 +1814,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0699</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="E12">
-        <v>0.0308</v>
+        <v>0.101</v>
       </c>
       <c r="F12">
-        <v>0.03</v>
+        <v>0.317</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1826,82 +1835,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>890.3</v>
+        <v>7592.1</v>
       </c>
       <c r="L12">
-        <v>0.3617341134405981</v>
+        <v>0.315963609728488</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>4523.247200000001</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.08487427547449503</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.5957834064356371</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>4523.247200000001</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.08487427547449503</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.5957834064356371</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>0</v>
+        <v>90585.3</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.699743871203805</v>
       </c>
       <c r="W12">
-        <v>0.07174689134411591</v>
+        <v>0.1234738768042285</v>
       </c>
       <c r="X12">
-        <v>0.2516095339167695</v>
+        <v>0.1796335504330748</v>
       </c>
       <c r="Y12">
-        <v>-0.1798626425726536</v>
+        <v>-0.05615967362884626</v>
       </c>
       <c r="Z12">
-        <v>0.05007507599155242</v>
+        <v>0.1113197949318555</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.09524696361502116</v>
+        <v>0.08003024278523135</v>
       </c>
       <c r="AC12">
-        <v>-0.09524696361502116</v>
+        <v>-0.08003024278523135</v>
       </c>
       <c r="AD12">
-        <v>42276.1</v>
+        <v>250928.2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>42276.1</v>
+        <v>250928.2</v>
       </c>
       <c r="AG12">
-        <v>42276.1</v>
+        <v>160342.9</v>
       </c>
       <c r="AH12">
-        <v>0.8384787782625942</v>
+        <v>0.8248201886979134</v>
       </c>
       <c r="AI12">
-        <v>0.8004381231516088</v>
+        <v>0.7856684382140747</v>
       </c>
       <c r="AJ12">
-        <v>0.8384787782625942</v>
+        <v>0.7505411062908756</v>
       </c>
       <c r="AK12">
-        <v>0.8004381231516088</v>
+        <v>0.7008101085462409</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1918,7 +1930,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
+          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1927,13 +1939,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0581</v>
+        <v>0.0747</v>
       </c>
       <c r="E13">
-        <v>-0.123</v>
+        <v>1.494</v>
       </c>
       <c r="F13">
-        <v>0.137</v>
+        <v>0.302</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1948,85 +1960,82 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>3395.8</v>
+        <v>1226.3</v>
       </c>
       <c r="L13">
-        <v>0.195662445117946</v>
+        <v>0.2627766944521825</v>
       </c>
       <c r="M13">
-        <v>2741.4</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.06754312914845494</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.8072913599151893</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>2741.4</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.06754312914845494</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.8072913599151893</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>116069.8</v>
+        <v>18645.9</v>
       </c>
       <c r="V13">
-        <v>2.859749577455072</v>
+        <v>2.339422606426358</v>
       </c>
       <c r="W13">
-        <v>0.0437395668033716</v>
+        <v>0.09942596766608831</v>
       </c>
       <c r="X13">
-        <v>0.3026543584529029</v>
+        <v>0.1944927223241224</v>
       </c>
       <c r="Y13">
-        <v>-0.2589147916495314</v>
+        <v>-0.09506675465803406</v>
       </c>
       <c r="Z13">
-        <v>0.04089992369294116</v>
+        <v>0.1036049836601307</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.09576722691730868</v>
+        <v>0.08111602104507268</v>
       </c>
       <c r="AC13">
-        <v>-0.09576722691730868</v>
+        <v>-0.08111602104507268</v>
       </c>
       <c r="AD13">
-        <v>274042</v>
+        <v>42593.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>274042</v>
+        <v>42593.5</v>
       </c>
       <c r="AG13">
-        <v>157972.2</v>
+        <v>23947.6</v>
       </c>
       <c r="AH13">
-        <v>0.8709993408117613</v>
+        <v>0.8423714198695509</v>
       </c>
       <c r="AI13">
-        <v>0.8162104332638767</v>
+        <v>0.7471757358874505</v>
       </c>
       <c r="AJ13">
-        <v>0.7955908452676174</v>
+        <v>0.7502874562549541</v>
       </c>
       <c r="AK13">
-        <v>0.7191033842954778</v>
+        <v>0.6242840868506599</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.104</v>
+        <v>0.14</v>
       </c>
       <c r="E2">
-        <v>0.226</v>
+        <v>0.2</v>
       </c>
       <c r="F2">
-        <v>0.139</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>23870.4</v>
+        <v>28282.2</v>
       </c>
       <c r="L2">
-        <v>0.3453237410071943</v>
+        <v>0.3920259149447561</v>
       </c>
       <c r="M2">
-        <v>4960.3244</v>
+        <v>6859.3423</v>
       </c>
       <c r="N2">
-        <v>0.03465721574033383</v>
+        <v>0.03807469183463786</v>
       </c>
       <c r="O2">
-        <v>0.2078023158388632</v>
+        <v>0.2425321332852466</v>
       </c>
       <c r="P2">
-        <v>4960.3244</v>
+        <v>6859.3423</v>
       </c>
       <c r="Q2">
-        <v>0.03465721574033383</v>
+        <v>0.03807469183463786</v>
       </c>
       <c r="R2">
-        <v>0.2078023158388632</v>
+        <v>0.2425321332852466</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>243049.9</v>
+        <v>131126.1</v>
       </c>
       <c r="V2">
-        <v>1.698161680709141</v>
+        <v>0.7278519762715309</v>
       </c>
       <c r="W2">
-        <v>0.146954986760812</v>
+        <v>0.1569980869655137</v>
       </c>
       <c r="X2">
-        <v>0.1796335504330748</v>
+        <v>0.1426818040536886</v>
       </c>
       <c r="Y2">
-        <v>-0.03267856367226277</v>
+        <v>0.01431628291182507</v>
       </c>
       <c r="Z2">
-        <v>0.1659565217234729</v>
+        <v>0.158809898187692</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0788301971896169</v>
+        <v>0.08032340140083621</v>
       </c>
       <c r="AC2">
-        <v>-0.0788301971896169</v>
+        <v>-0.08032340140083621</v>
       </c>
       <c r="AD2">
-        <v>540294.4</v>
+        <v>572583.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>540294.4</v>
+        <v>572583.6</v>
       </c>
       <c r="AG2">
-        <v>297244.5</v>
+        <v>441457.5</v>
       </c>
       <c r="AH2">
-        <v>0.7905748107641616</v>
+        <v>0.7606673499495509</v>
       </c>
       <c r="AI2">
-        <v>0.7382114820879728</v>
+        <v>0.7464479804327515</v>
       </c>
       <c r="AJ2">
-        <v>0.6749883847620796</v>
+        <v>0.7101812962547079</v>
       </c>
       <c r="AK2">
-        <v>0.6080527101957957</v>
+        <v>0.6941683926890034</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.14</v>
+        <v>0.152</v>
       </c>
       <c r="E3">
-        <v>0.192</v>
+        <v>0.2</v>
       </c>
       <c r="F3">
-        <v>0.124</v>
+        <v>0.00132</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>614.2</v>
+        <v>719.3</v>
       </c>
       <c r="L3">
-        <v>0.4951628506933247</v>
+        <v>0.4964455794050658</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1902.9</v>
+        <v>3193.2</v>
       </c>
       <c r="V3">
-        <v>0.2075611644978676</v>
+        <v>0.3006949545172043</v>
       </c>
       <c r="W3">
-        <v>0.349294813466788</v>
+        <v>0.3305454712559165</v>
       </c>
       <c r="X3">
-        <v>0.07171592818007219</v>
+        <v>0.07633558444182739</v>
       </c>
       <c r="Y3">
-        <v>0.2775788852867158</v>
+        <v>0.2542098868140892</v>
       </c>
       <c r="Z3">
-        <v>2.400154798761611</v>
+        <v>1.415356061346098</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07063199552625604</v>
+        <v>0.07503947159909945</v>
       </c>
       <c r="AC3">
-        <v>-0.07063199552625604</v>
+        <v>-0.07503947159909945</v>
       </c>
       <c r="AD3">
-        <v>845.3</v>
+        <v>944.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>845.3</v>
+        <v>944.8</v>
       </c>
       <c r="AG3">
-        <v>-1057.6</v>
+        <v>-2248.4</v>
       </c>
       <c r="AH3">
-        <v>0.08441856749091201</v>
+        <v>0.08170042026253438</v>
       </c>
       <c r="AI3">
-        <v>0.2797709671013437</v>
+        <v>0.2629923451635351</v>
       </c>
       <c r="AJ3">
-        <v>-0.1304020813040208</v>
+        <v>-0.2685939553219447</v>
       </c>
       <c r="AK3">
-        <v>-0.9455520786767996</v>
+        <v>-5.630853994490355</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credito Emiliano S.p.A. (BIT:CE)</t>
+          <t>UniCredit S.p.A. (BIT:UCG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.108</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="E4">
-        <v>0.226</v>
+        <v>0.114</v>
       </c>
       <c r="F4">
-        <v>0.111</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +856,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>560.9</v>
+        <v>11778.9</v>
       </c>
       <c r="L4">
-        <v>0.2999625648430397</v>
+        <v>0.4401319771917107</v>
       </c>
       <c r="M4">
-        <v>118.6949</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03927043837882548</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.2116150829024782</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>118.6949</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03927043837882548</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2116150829024782</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>6091.3</v>
+        <v>42856.3</v>
       </c>
       <c r="V4">
-        <v>2.015318444995864</v>
+        <v>0.6977160281780486</v>
       </c>
       <c r="W4">
-        <v>0.1827869386690999</v>
+        <v>0.1774176542533001</v>
       </c>
       <c r="X4">
-        <v>0.1589650593724325</v>
+        <v>0.1208146907792201</v>
       </c>
       <c r="Y4">
-        <v>0.02382187929666738</v>
+        <v>0.05660296347408003</v>
       </c>
       <c r="Z4">
-        <v>0.1577841532360139</v>
+        <v>0.2668140869447314</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07451323648074738</v>
+        <v>0.07971849988878377</v>
       </c>
       <c r="AC4">
-        <v>-0.07451323648074738</v>
+        <v>-0.07971849988878377</v>
       </c>
       <c r="AD4">
-        <v>11559</v>
+        <v>131151</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11559</v>
+        <v>131151</v>
       </c>
       <c r="AG4">
-        <v>5467.7</v>
+        <v>88294.7</v>
       </c>
       <c r="AH4">
-        <v>0.7927167986832631</v>
+        <v>0.6810396173536815</v>
       </c>
       <c r="AI4">
-        <v>0.7458092989044172</v>
+        <v>0.6480679421047248</v>
       </c>
       <c r="AJ4">
-        <v>0.6440013191679819</v>
+        <v>0.589738469019172</v>
       </c>
       <c r="AK4">
-        <v>0.5812188406875511</v>
+        <v>0.5535162616916172</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banca Popolare di Sondrio S.p.A (BIT:BPSO)</t>
+          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,13 +957,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.132</v>
+        <v>0.146</v>
       </c>
       <c r="E5">
-        <v>0.291</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F5">
-        <v>0.135</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,85 +978,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>474.8</v>
+        <v>2249.4</v>
       </c>
       <c r="L5">
-        <v>0.3644458090267117</v>
+        <v>0.4039435405667492</v>
       </c>
       <c r="M5">
-        <v>133.1112</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04569714030691063</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.280352148272957</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>133.1112</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.04569714030691063</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.280352148272957</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>3867</v>
+        <v>10126</v>
       </c>
       <c r="V5">
-        <v>1.327542998386488</v>
+        <v>0.8339098066343842</v>
       </c>
       <c r="W5">
-        <v>0.14581413918064</v>
+        <v>0.1560761021911991</v>
       </c>
       <c r="X5">
-        <v>0.1884324154705405</v>
+        <v>0.1383062169845482</v>
       </c>
       <c r="Y5">
-        <v>-0.04261827628990053</v>
+        <v>0.01776988520665096</v>
       </c>
       <c r="Z5">
-        <v>0.1131138431617698</v>
+        <v>0.1451675973284532</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07478151524743974</v>
+        <v>0.0802270825272535</v>
       </c>
       <c r="AC5">
-        <v>-0.07478151524743974</v>
+        <v>-0.0802270825272535</v>
       </c>
       <c r="AD5">
-        <v>14811.5</v>
+        <v>35698.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14811.5</v>
+        <v>35698.2</v>
       </c>
       <c r="AG5">
-        <v>10944.5</v>
+        <v>25572.2</v>
       </c>
       <c r="AH5">
-        <v>0.8356559319356367</v>
+        <v>0.7461842352793628</v>
       </c>
       <c r="AI5">
-        <v>0.7929195865029952</v>
+        <v>0.6811593649824453</v>
       </c>
       <c r="AJ5">
-        <v>0.7897946223678324</v>
+        <v>0.6780379159485616</v>
       </c>
       <c r="AK5">
-        <v>0.7388592221539625</v>
+        <v>0.6048010973936899</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco di Desio e della Brianza S.p.A. (BIT:BDB)</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A. (BIT:MB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1079,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.08939999999999999</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="E6">
-        <v>0.434</v>
+        <v>0.081</v>
+      </c>
+      <c r="F6">
+        <v>0.0864</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>257.4</v>
+        <v>1396.5</v>
       </c>
       <c r="L6">
-        <v>0.4941447494720675</v>
+        <v>0.3830119854090672</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1130,55 +1127,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2715.3</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>5.022752497225305</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.2377389858686617</v>
+        <v>0.1215923239675754</v>
       </c>
       <c r="X6">
-        <v>0.3153746443777281</v>
+        <v>0.1426818040536886</v>
       </c>
       <c r="Y6">
-        <v>-0.0776356585090664</v>
+        <v>-0.02108948008611322</v>
       </c>
       <c r="Z6">
-        <v>0.08184717879421147</v>
+        <v>0.07918489143323762</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07526572195836997</v>
+        <v>0.08032340140083621</v>
       </c>
       <c r="AC6">
-        <v>-0.07526572195836997</v>
+        <v>-0.08032340140083621</v>
       </c>
       <c r="AD6">
-        <v>5684.3</v>
+        <v>37838.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>5684.3</v>
+        <v>37838.1</v>
       </c>
       <c r="AG6">
-        <v>2969</v>
+        <v>37838.1</v>
       </c>
       <c r="AH6">
-        <v>0.9131552314093399</v>
+        <v>0.7585217705075775</v>
       </c>
       <c r="AI6">
-        <v>0.8019044931932002</v>
+        <v>0.7530689498698383</v>
       </c>
       <c r="AJ6">
-        <v>0.8459653521768863</v>
+        <v>0.7585217705075775</v>
       </c>
       <c r="AK6">
-        <v>0.6789078935333395</v>
+        <v>0.7530689498698383</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banca Sistema S.p.A. (BIT:BST)</t>
+          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,10 +1201,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0309</v>
+        <v>0.0964</v>
       </c>
       <c r="E7">
-        <v>-0.08380000000000001</v>
+        <v>0.151</v>
+      </c>
+      <c r="F7">
+        <v>0.0643</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,28 +1222,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>16.5</v>
+        <v>9780.299999999999</v>
       </c>
       <c r="L7">
-        <v>0.1722338204592902</v>
+        <v>0.3570299523609615</v>
       </c>
       <c r="M7">
-        <v>5.5407</v>
+        <v>6383.8098</v>
       </c>
       <c r="N7">
-        <v>0.05207424812030075</v>
+        <v>0.08976400811612299</v>
       </c>
       <c r="O7">
-        <v>0.3358</v>
+        <v>0.6527212662188276</v>
       </c>
       <c r="P7">
-        <v>5.5407</v>
+        <v>6383.8098</v>
       </c>
       <c r="Q7">
-        <v>0.05207424812030075</v>
+        <v>0.08976400811612299</v>
       </c>
       <c r="R7">
-        <v>0.3358</v>
+        <v>0.6527212662188276</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1252,55 +1252,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>164</v>
+        <v>62537.4</v>
       </c>
       <c r="V7">
-        <v>1.541353383458647</v>
+        <v>0.8793507101607617</v>
       </c>
       <c r="W7">
-        <v>0.06947368421052631</v>
+        <v>0.1432379273023912</v>
       </c>
       <c r="X7">
-        <v>0.3870081024947167</v>
+        <v>0.1739157145365404</v>
       </c>
       <c r="Y7">
-        <v>-0.3175344182841904</v>
+        <v>-0.0306777872341493</v>
       </c>
       <c r="Z7">
-        <v>0.05864707682889501</v>
+        <v>0.1218910951665832</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07537976279662342</v>
+        <v>0.08080902619640799</v>
       </c>
       <c r="AC7">
-        <v>-0.07537976279662342</v>
+        <v>-0.08080902619640799</v>
       </c>
       <c r="AD7">
-        <v>1444.8</v>
+        <v>325580</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1444.8</v>
+        <v>325580</v>
       </c>
       <c r="AG7">
-        <v>1280.8</v>
+        <v>263042.6</v>
       </c>
       <c r="AH7">
-        <v>0.9314079422382671</v>
+        <v>0.8207257062493682</v>
       </c>
       <c r="AI7">
-        <v>0.83664369679773</v>
+        <v>0.8128053668421445</v>
       </c>
       <c r="AJ7">
-        <v>0.9232987312572087</v>
+        <v>0.7871748977960578</v>
       </c>
       <c r="AK7">
-        <v>0.8195022074348965</v>
+        <v>0.7781729151523596</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UniCredit S.p.A. (BIT:UCG)</t>
+          <t>Banca Popolare di Sondrio S.p.A (BIT:BPSO)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.073</v>
+        <v>0.14</v>
       </c>
       <c r="E8">
-        <v>0.253</v>
+        <v>0.285</v>
       </c>
       <c r="F8">
-        <v>0.295</v>
+        <v>-0.0583</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>9695.200000000001</v>
+        <v>607.3</v>
       </c>
       <c r="L8">
-        <v>0.4082189473684211</v>
+        <v>0.3921859864384888</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1374,55 +1374,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>92506.39999999999</v>
+        <v>2473.1</v>
       </c>
       <c r="V8">
-        <v>1.980246004461132</v>
+        <v>0.6524469067405355</v>
       </c>
       <c r="W8">
-        <v>0.1569391745768638</v>
+        <v>0.1569980869655137</v>
       </c>
       <c r="X8">
-        <v>0.1328571873788326</v>
+        <v>0.1429979720506709</v>
       </c>
       <c r="Y8">
-        <v>0.02408198719803126</v>
+        <v>0.01400011491484282</v>
       </c>
       <c r="Z8">
-        <v>0.4510295818433532</v>
+        <v>0.1046658600715121</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0788301971896169</v>
+        <v>0.08148423742172903</v>
       </c>
       <c r="AC8">
-        <v>-0.0788301971896169</v>
+        <v>-0.08148423742172903</v>
       </c>
       <c r="AD8">
-        <v>126481.8</v>
+        <v>11961.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>126481.8</v>
+        <v>11961.7</v>
       </c>
       <c r="AG8">
-        <v>33975.40000000001</v>
+        <v>9488.6</v>
       </c>
       <c r="AH8">
-        <v>0.730279613202122</v>
+        <v>0.7593669455695078</v>
       </c>
       <c r="AI8">
-        <v>0.6551536413913632</v>
+        <v>0.727615027129614</v>
       </c>
       <c r="AJ8">
-        <v>0.4210608501673071</v>
+        <v>0.714551437973959</v>
       </c>
       <c r="AK8">
-        <v>0.3378945662021894</v>
+        <v>0.6793828088640677</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="E9">
         <v>0.226</v>
       </c>
       <c r="F9">
-        <v>0.4370000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1469,28 +1469,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1132.2</v>
+        <v>1750.5</v>
       </c>
       <c r="L9">
-        <v>0.2229969274403215</v>
+        <v>0.3030696514828858</v>
       </c>
       <c r="M9">
-        <v>179.7304</v>
+        <v>475.5325</v>
       </c>
       <c r="N9">
-        <v>0.03797067646934551</v>
+        <v>0.05274961452706076</v>
       </c>
       <c r="O9">
-        <v>0.1587443914502738</v>
+        <v>0.2716552413596116</v>
       </c>
       <c r="P9">
-        <v>179.7304</v>
+        <v>475.5325</v>
       </c>
       <c r="Q9">
-        <v>0.03797067646934551</v>
+        <v>0.05274961452706076</v>
       </c>
       <c r="R9">
-        <v>0.1587443914502738</v>
+        <v>0.2716552413596116</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1499,548 +1499,60 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>12267.7</v>
+        <v>9940.1</v>
       </c>
       <c r="V9">
-        <v>2.59173110237884</v>
+        <v>1.102630090184029</v>
       </c>
       <c r="W9">
-        <v>0.146954986760812</v>
+        <v>0.1865846639237673</v>
       </c>
       <c r="X9">
-        <v>0.2281410648259944</v>
+        <v>0.1453162382371421</v>
       </c>
       <c r="Y9">
-        <v>-0.08118607806518241</v>
+        <v>0.04126842568662523</v>
       </c>
       <c r="Z9">
-        <v>0.2774153361964397</v>
+        <v>0.1990783505438904</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07885520450028874</v>
+        <v>0.08154039462781529</v>
       </c>
       <c r="AC9">
-        <v>-0.07885520450028874</v>
+        <v>-0.08154039462781529</v>
       </c>
       <c r="AD9">
-        <v>32108.3</v>
+        <v>29409.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>32108.3</v>
+        <v>29409.8</v>
       </c>
       <c r="AG9">
-        <v>19840.6</v>
+        <v>19469.7</v>
       </c>
       <c r="AH9">
-        <v>0.871520586726454</v>
+        <v>0.7653878885196241</v>
       </c>
       <c r="AI9">
-        <v>0.7701512800155429</v>
+        <v>0.7094083479670403</v>
       </c>
       <c r="AJ9">
-        <v>0.8073817856270855</v>
+        <v>0.6835167072734039</v>
       </c>
       <c r="AK9">
-        <v>0.6743182250740912</v>
+        <v>0.6177582043805347</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A. (BIT:MB)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.104</v>
-      </c>
-      <c r="E10">
-        <v>0.0665</v>
-      </c>
-      <c r="F10">
-        <v>0.139</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>1180.7</v>
-      </c>
-      <c r="L10">
-        <v>0.3674644424387663</v>
-      </c>
-      <c r="M10">
-        <v>-0</v>
-      </c>
-      <c r="N10">
-        <v>-0</v>
-      </c>
-      <c r="O10">
-        <v>-0</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>-0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0.1130884536181217</v>
-      </c>
-      <c r="X10">
-        <v>0.1470837726097598</v>
-      </c>
-      <c r="Y10">
-        <v>-0.03399531899163806</v>
-      </c>
-      <c r="Z10">
-        <v>0.06098352566049195</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.07931291944586655</v>
-      </c>
-      <c r="AC10">
-        <v>-0.07931291944586655</v>
-      </c>
-      <c r="AD10">
-        <v>34560.3</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>34560.3</v>
-      </c>
-      <c r="AG10">
-        <v>34560.3</v>
-      </c>
-      <c r="AH10">
-        <v>0.7683088681548076</v>
-      </c>
-      <c r="AI10">
-        <v>0.7489305728315657</v>
-      </c>
-      <c r="AJ10">
-        <v>0.7683088681548076</v>
-      </c>
-      <c r="AK10">
-        <v>0.7489305728315657</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A. (BIT:BMPS)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.11</v>
-      </c>
-      <c r="F11">
-        <v>0.12</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>1120.1</v>
-      </c>
-      <c r="L11">
-        <v>0.3334127102247358</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="O11">
-        <v>-0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>-0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>14304.1</v>
-      </c>
-      <c r="V11">
-        <v>3.372653965858719</v>
-      </c>
-      <c r="W11">
-        <v>0.2153582895925862</v>
-      </c>
-      <c r="X11">
-        <v>0.1758194379058632</v>
-      </c>
-      <c r="Y11">
-        <v>0.03953885168672294</v>
-      </c>
-      <c r="Z11">
-        <v>33.84886649873993</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.07996482010825361</v>
-      </c>
-      <c r="AC11">
-        <v>-0.07996482010825361</v>
-      </c>
-      <c r="AD11">
-        <v>19277.4</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>19277.4</v>
-      </c>
-      <c r="AG11">
-        <v>4973.300000000001</v>
-      </c>
-      <c r="AH11">
-        <v>0.819666136589763</v>
-      </c>
-      <c r="AI11">
-        <v>0.674039678599151</v>
-      </c>
-      <c r="AJ11">
-        <v>0.5397254327418743</v>
-      </c>
-      <c r="AK11">
-        <v>0.3478878264093399</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.08289999999999999</v>
-      </c>
-      <c r="E12">
-        <v>0.101</v>
-      </c>
-      <c r="F12">
-        <v>0.317</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>7592.1</v>
-      </c>
-      <c r="L12">
-        <v>0.315963609728488</v>
-      </c>
-      <c r="M12">
-        <v>4523.247200000001</v>
-      </c>
-      <c r="N12">
-        <v>0.08487427547449503</v>
-      </c>
-      <c r="O12">
-        <v>0.5957834064356371</v>
-      </c>
-      <c r="P12">
-        <v>4523.247200000001</v>
-      </c>
-      <c r="Q12">
-        <v>0.08487427547449503</v>
-      </c>
-      <c r="R12">
-        <v>0.5957834064356371</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>90585.3</v>
-      </c>
-      <c r="V12">
-        <v>1.699743871203805</v>
-      </c>
-      <c r="W12">
-        <v>0.1234738768042285</v>
-      </c>
-      <c r="X12">
-        <v>0.1796335504330748</v>
-      </c>
-      <c r="Y12">
-        <v>-0.05615967362884626</v>
-      </c>
-      <c r="Z12">
-        <v>0.1113197949318555</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.08003024278523135</v>
-      </c>
-      <c r="AC12">
-        <v>-0.08003024278523135</v>
-      </c>
-      <c r="AD12">
-        <v>250928.2</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>250928.2</v>
-      </c>
-      <c r="AG12">
-        <v>160342.9</v>
-      </c>
-      <c r="AH12">
-        <v>0.8248201886979134</v>
-      </c>
-      <c r="AI12">
-        <v>0.7856684382140747</v>
-      </c>
-      <c r="AJ12">
-        <v>0.7505411062908756</v>
-      </c>
-      <c r="AK12">
-        <v>0.7008101085462409</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0747</v>
-      </c>
-      <c r="E13">
-        <v>1.494</v>
-      </c>
-      <c r="F13">
-        <v>0.302</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>1226.3</v>
-      </c>
-      <c r="L13">
-        <v>0.2627766944521825</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>-0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>-0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>18645.9</v>
-      </c>
-      <c r="V13">
-        <v>2.339422606426358</v>
-      </c>
-      <c r="W13">
-        <v>0.09942596766608831</v>
-      </c>
-      <c r="X13">
-        <v>0.1944927223241224</v>
-      </c>
-      <c r="Y13">
-        <v>-0.09506675465803406</v>
-      </c>
-      <c r="Z13">
-        <v>0.1036049836601307</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.08111602104507268</v>
-      </c>
-      <c r="AC13">
-        <v>-0.08111602104507268</v>
-      </c>
-      <c r="AD13">
-        <v>42593.5</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>42593.5</v>
-      </c>
-      <c r="AG13">
-        <v>23947.6</v>
-      </c>
-      <c r="AH13">
-        <v>0.8423714198695509</v>
-      </c>
-      <c r="AI13">
-        <v>0.7471757358874505</v>
-      </c>
-      <c r="AJ13">
-        <v>0.7502874562549541</v>
-      </c>
-      <c r="AK13">
-        <v>0.6242840868506599</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.14</v>
+        <v>0.107</v>
       </c>
       <c r="E2">
-        <v>0.2</v>
+        <v>0.226</v>
       </c>
       <c r="F2">
-        <v>0.06909999999999999</v>
+        <v>0.0643</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>28282.2</v>
+        <v>32126.3</v>
       </c>
       <c r="L2">
-        <v>0.3920259149447561</v>
+        <v>0.4065735055152549</v>
       </c>
       <c r="M2">
-        <v>6859.3423</v>
+        <v>7380.1322</v>
       </c>
       <c r="N2">
-        <v>0.03807469183463786</v>
+        <v>0.03806558200613371</v>
       </c>
       <c r="O2">
-        <v>0.2425321332852466</v>
+        <v>0.2297224454730237</v>
       </c>
       <c r="P2">
-        <v>6859.3423</v>
+        <v>7380.1322</v>
       </c>
       <c r="Q2">
-        <v>0.03807469183463786</v>
+        <v>0.03806558200613371</v>
       </c>
       <c r="R2">
-        <v>0.2425321332852466</v>
+        <v>0.2297224454730237</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>131126.1</v>
+        <v>150361.2</v>
       </c>
       <c r="V2">
-        <v>0.7278519762715309</v>
+        <v>0.7755398459042065</v>
       </c>
       <c r="W2">
         <v>0.1569980869655137</v>
       </c>
       <c r="X2">
-        <v>0.1426818040536886</v>
+        <v>0.1426636583274014</v>
       </c>
       <c r="Y2">
-        <v>0.01431628291182507</v>
+        <v>0.01433442863811232</v>
       </c>
       <c r="Z2">
-        <v>0.158809898187692</v>
+        <v>0.1634153943997202</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08032340140083621</v>
+        <v>0.07991048668066913</v>
       </c>
       <c r="AC2">
-        <v>-0.08032340140083621</v>
+        <v>-0.07991048668066913</v>
       </c>
       <c r="AD2">
-        <v>572583.6</v>
+        <v>610248.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>572583.6</v>
+        <v>610248.6</v>
       </c>
       <c r="AG2">
-        <v>441457.5</v>
+        <v>459887.4</v>
       </c>
       <c r="AH2">
-        <v>0.7606673499495509</v>
+        <v>0.7588948525607863</v>
       </c>
       <c r="AI2">
-        <v>0.7464479804327515</v>
+        <v>0.7406932783614868</v>
       </c>
       <c r="AJ2">
-        <v>0.7101812962547079</v>
+        <v>0.7034425731009896</v>
       </c>
       <c r="AK2">
-        <v>0.6941683926890034</v>
+        <v>0.6828044954977319</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -770,10 +770,10 @@
         <v>0.3305454712559165</v>
       </c>
       <c r="X3">
-        <v>0.07633558444182739</v>
+        <v>0.07632986520112256</v>
       </c>
       <c r="Y3">
-        <v>0.2542098868140892</v>
+        <v>0.254215606054794</v>
       </c>
       <c r="Z3">
         <v>1.415356061346098</v>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07503947159909945</v>
+        <v>0.07503421962276378</v>
       </c>
       <c r="AC3">
-        <v>-0.07503947159909945</v>
+        <v>-0.07503421962276378</v>
       </c>
       <c r="AD3">
         <v>944.8</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UniCredit S.p.A. (BIT:UCG)</t>
+          <t>Credito Emiliano S.p.A. (BIT:CE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.08410000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="E4">
-        <v>0.114</v>
+        <v>0.258</v>
       </c>
       <c r="F4">
-        <v>0.08529999999999999</v>
+        <v>-0.0453</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,82 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>11778.9</v>
+        <v>679.2</v>
       </c>
       <c r="L4">
-        <v>0.4401319771917107</v>
+        <v>0.3193830527602747</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>169.3246</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04456027790205006</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2493000588928151</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>169.3246</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04456027790205006</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2493000588928151</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>42856.3</v>
+        <v>3305.4</v>
       </c>
       <c r="V4">
-        <v>0.6977160281780486</v>
+        <v>0.8698649964472749</v>
       </c>
       <c r="W4">
-        <v>0.1774176542533001</v>
+        <v>0.1724076659474553</v>
       </c>
       <c r="X4">
-        <v>0.1208146907792201</v>
+        <v>0.1344975229993139</v>
       </c>
       <c r="Y4">
-        <v>0.05660296347408003</v>
+        <v>0.03791014294814141</v>
       </c>
       <c r="Z4">
-        <v>0.2668140869447314</v>
+        <v>0.2337231283246142</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07971849988878377</v>
+        <v>0.07678188769911662</v>
       </c>
       <c r="AC4">
-        <v>-0.07971849988878377</v>
+        <v>-0.07678188769911662</v>
       </c>
       <c r="AD4">
-        <v>131151</v>
+        <v>10508.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>131151</v>
+        <v>10508.3</v>
       </c>
       <c r="AG4">
-        <v>88294.7</v>
+        <v>7202.9</v>
       </c>
       <c r="AH4">
-        <v>0.6810396173536815</v>
+        <v>0.7344250150263485</v>
       </c>
       <c r="AI4">
-        <v>0.6480679421047248</v>
+        <v>0.6935713814269685</v>
       </c>
       <c r="AJ4">
-        <v>0.589738469019172</v>
+        <v>0.6546424546479078</v>
       </c>
       <c r="AK4">
-        <v>0.5535162616916172</v>
+        <v>0.6080654420206659</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
+          <t>Banco di Desio e della Brianza S.p.A. (BIT:BDB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,13 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.146</v>
+        <v>0.107</v>
       </c>
       <c r="E5">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="F5">
-        <v>0.06909999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2249.4</v>
+        <v>146.2</v>
       </c>
       <c r="L5">
-        <v>0.4039435405667492</v>
+        <v>0.2371836469824789</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1005,55 +1005,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>10126</v>
+        <v>488.3</v>
       </c>
       <c r="V5">
-        <v>0.8339098066343842</v>
+        <v>0.5177605768211219</v>
       </c>
       <c r="W5">
-        <v>0.1560761021911991</v>
+        <v>0.1041162227602905</v>
       </c>
       <c r="X5">
-        <v>0.1383062169845482</v>
+        <v>0.1721944104572656</v>
       </c>
       <c r="Y5">
-        <v>0.01776988520665096</v>
+        <v>-0.06807818769697509</v>
       </c>
       <c r="Z5">
-        <v>0.1451675973284532</v>
+        <v>0.141473490934129</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0802270825272535</v>
+        <v>0.07705394623888281</v>
       </c>
       <c r="AC5">
-        <v>-0.0802270825272535</v>
+        <v>-0.07705394623888281</v>
       </c>
       <c r="AD5">
-        <v>35698.2</v>
+        <v>4243.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>35698.2</v>
+        <v>4243.9</v>
       </c>
       <c r="AG5">
-        <v>25572.2</v>
+        <v>3755.599999999999</v>
       </c>
       <c r="AH5">
-        <v>0.7461842352793628</v>
+        <v>0.8181800655484865</v>
       </c>
       <c r="AI5">
-        <v>0.6811593649824453</v>
+        <v>0.7250935433716619</v>
       </c>
       <c r="AJ5">
-        <v>0.6780379159485616</v>
+        <v>0.7992849085917381</v>
       </c>
       <c r="AK5">
-        <v>0.6048010973936899</v>
+        <v>0.7000708347313872</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A. (BIT:MB)</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A. (BIT:BMPS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.07980000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="E6">
-        <v>0.081</v>
+        <v>0.99</v>
       </c>
       <c r="F6">
-        <v>0.0864</v>
+        <v>0.0179</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,82 +1100,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1396.5</v>
+        <v>2999.2</v>
       </c>
       <c r="L6">
-        <v>0.3830119854090672</v>
+        <v>0.7486209220477746</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>351.4563000000001</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.03959580221043026</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.1171833488930382</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>351.4563000000001</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.03959580221043026</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.1171833488930382</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0</v>
+        <v>15318.2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.725780466646387</v>
       </c>
       <c r="W6">
-        <v>0.1215923239675754</v>
+        <v>0.3217438879174399</v>
       </c>
       <c r="X6">
-        <v>0.1426818040536886</v>
+        <v>0.1268870827265033</v>
       </c>
       <c r="Y6">
-        <v>-0.02108948008611322</v>
+        <v>0.1948568051909366</v>
       </c>
       <c r="Z6">
-        <v>0.07918489143323762</v>
+        <v>0.2804228286007067</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08032340140083621</v>
+        <v>0.07857457431472775</v>
       </c>
       <c r="AC6">
-        <v>-0.08032340140083621</v>
+        <v>-0.07857457431472775</v>
       </c>
       <c r="AD6">
-        <v>37838.1</v>
+        <v>21437.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>37838.1</v>
+        <v>21437.9</v>
       </c>
       <c r="AG6">
-        <v>37838.1</v>
+        <v>6119.700000000001</v>
       </c>
       <c r="AH6">
-        <v>0.7585217705075775</v>
+        <v>0.7071946955202217</v>
       </c>
       <c r="AI6">
-        <v>0.7530689498698383</v>
+        <v>0.6304819659788721</v>
       </c>
       <c r="AJ6">
-        <v>0.7585217705075775</v>
+        <v>0.4080942663945905</v>
       </c>
       <c r="AK6">
-        <v>0.7530689498698383</v>
+        <v>0.3275334239624924</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
+          <t>UniCredit S.p.A. (BIT:UCG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,13 +1204,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0964</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="E7">
-        <v>0.151</v>
+        <v>0.114</v>
       </c>
       <c r="F7">
-        <v>0.0643</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,85 +1225,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>9780.299999999999</v>
+        <v>11778.9</v>
       </c>
       <c r="L7">
-        <v>0.3570299523609615</v>
+        <v>0.4401319771917107</v>
       </c>
       <c r="M7">
-        <v>6383.8098</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.08976400811612299</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.6527212662188276</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>6383.8098</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.08976400811612299</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.6527212662188276</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>62537.4</v>
+        <v>42856.3</v>
       </c>
       <c r="V7">
-        <v>0.8793507101607617</v>
+        <v>0.6977160281780486</v>
       </c>
       <c r="W7">
-        <v>0.1432379273023912</v>
+        <v>0.1774176542533001</v>
       </c>
       <c r="X7">
-        <v>0.1739157145365404</v>
+        <v>0.1208006407100694</v>
       </c>
       <c r="Y7">
-        <v>-0.0306777872341493</v>
+        <v>0.05661701354323076</v>
       </c>
       <c r="Z7">
-        <v>0.1218910951665832</v>
+        <v>0.2668140869447314</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08080902619640799</v>
+        <v>0.07971401847335124</v>
       </c>
       <c r="AC7">
-        <v>-0.08080902619640799</v>
+        <v>-0.07971401847335124</v>
       </c>
       <c r="AD7">
-        <v>325580</v>
+        <v>131151</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>325580</v>
+        <v>131151</v>
       </c>
       <c r="AG7">
-        <v>263042.6</v>
+        <v>88294.7</v>
       </c>
       <c r="AH7">
-        <v>0.8207257062493682</v>
+        <v>0.6810396173536815</v>
       </c>
       <c r="AI7">
-        <v>0.8128053668421445</v>
+        <v>0.6480679421047248</v>
       </c>
       <c r="AJ7">
-        <v>0.7871748977960578</v>
+        <v>0.589738469019172</v>
       </c>
       <c r="AK7">
-        <v>0.7781729151523596</v>
+        <v>0.5535162616916172</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Banca Popolare di Sondrio S.p.A (BIT:BPSO)</t>
+          <t>Banca Sistema S.p.A. (BIT:BST)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,13 +1326,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.14</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="E8">
-        <v>0.285</v>
-      </c>
-      <c r="F8">
-        <v>-0.0583</v>
+        <v>-0.0993</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,82 +1344,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>607.3</v>
+        <v>19.5</v>
       </c>
       <c r="L8">
-        <v>0.3921859864384888</v>
+        <v>0.1570048309178744</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>8.538899430740037E-05</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.0004615384615384615</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>8.538899430740037E-05</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.0004615384615384615</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>2473.1</v>
+        <v>123.2</v>
       </c>
       <c r="V8">
-        <v>0.6524469067405355</v>
+        <v>1.16888045540797</v>
       </c>
       <c r="W8">
-        <v>0.1569980869655137</v>
+        <v>0.07195571955719557</v>
       </c>
       <c r="X8">
-        <v>0.1429979720506709</v>
+        <v>0.3785163746053329</v>
       </c>
       <c r="Y8">
-        <v>0.01400011491484282</v>
+        <v>-0.3065606550481373</v>
       </c>
       <c r="Z8">
-        <v>0.1046658600715121</v>
+        <v>0.08190991228648685</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08148423742172903</v>
+        <v>0.07991048668066913</v>
       </c>
       <c r="AC8">
-        <v>-0.08148423742172903</v>
+        <v>-0.07991048668066913</v>
       </c>
       <c r="AD8">
-        <v>11961.7</v>
+        <v>1474.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>11961.7</v>
+        <v>1474.9</v>
       </c>
       <c r="AG8">
-        <v>9488.6</v>
+        <v>1351.7</v>
       </c>
       <c r="AH8">
-        <v>0.7593669455695078</v>
+        <v>0.9333038030753654</v>
       </c>
       <c r="AI8">
-        <v>0.727615027129614</v>
+        <v>0.8173908224340501</v>
       </c>
       <c r="AJ8">
-        <v>0.714551437973959</v>
+        <v>0.9276645391531123</v>
       </c>
       <c r="AK8">
-        <v>0.6793828088640677</v>
+        <v>0.8040090411610754</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,120 +1439,611 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Banco BPM S.p.A. (BIT:BAMI)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.146</v>
+      </c>
+      <c r="E9">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>2249.4</v>
+      </c>
+      <c r="L9">
+        <v>0.4039435405667492</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>10126</v>
+      </c>
+      <c r="V9">
+        <v>0.8339098066343842</v>
+      </c>
+      <c r="W9">
+        <v>0.1560761021911991</v>
+      </c>
+      <c r="X9">
+        <v>0.1382888907950777</v>
+      </c>
+      <c r="Y9">
+        <v>0.01778721139612141</v>
+      </c>
+      <c r="Z9">
+        <v>0.1451675973284532</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.08022268486722337</v>
+      </c>
+      <c r="AC9">
+        <v>-0.08022268486722337</v>
+      </c>
+      <c r="AD9">
+        <v>35698.2</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>35698.2</v>
+      </c>
+      <c r="AG9">
+        <v>25572.2</v>
+      </c>
+      <c r="AH9">
+        <v>0.7461842352793628</v>
+      </c>
+      <c r="AI9">
+        <v>0.6811593649824453</v>
+      </c>
+      <c r="AJ9">
+        <v>0.6780379159485616</v>
+      </c>
+      <c r="AK9">
+        <v>0.6048010973936899</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A. (BIT:MB)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="E10">
+        <v>0.081</v>
+      </c>
+      <c r="F10">
+        <v>0.0864</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1396.5</v>
+      </c>
+      <c r="L10">
+        <v>0.3830119854090672</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.1215923239675754</v>
+      </c>
+      <c r="X10">
+        <v>0.1426636583274014</v>
+      </c>
+      <c r="Y10">
+        <v>-0.02107133435982597</v>
+      </c>
+      <c r="Z10">
+        <v>0.07918489143323762</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.08031901960297952</v>
+      </c>
+      <c r="AC10">
+        <v>-0.08031901960297952</v>
+      </c>
+      <c r="AD10">
+        <v>37838.1</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>37838.1</v>
+      </c>
+      <c r="AG10">
+        <v>37838.1</v>
+      </c>
+      <c r="AH10">
+        <v>0.7585217705075775</v>
+      </c>
+      <c r="AI10">
+        <v>0.7530689498698383</v>
+      </c>
+      <c r="AJ10">
+        <v>0.7585217705075775</v>
+      </c>
+      <c r="AK10">
+        <v>0.7530689498698383</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo S.p.A. (BIT:ISP)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0964</v>
+      </c>
+      <c r="E11">
+        <v>0.151</v>
+      </c>
+      <c r="F11">
+        <v>0.0643</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>9780.299999999999</v>
+      </c>
+      <c r="L11">
+        <v>0.3570299523609615</v>
+      </c>
+      <c r="M11">
+        <v>6383.8098</v>
+      </c>
+      <c r="N11">
+        <v>0.08976400811612299</v>
+      </c>
+      <c r="O11">
+        <v>0.6527212662188276</v>
+      </c>
+      <c r="P11">
+        <v>6383.8098</v>
+      </c>
+      <c r="Q11">
+        <v>0.08976400811612299</v>
+      </c>
+      <c r="R11">
+        <v>0.6527212662188276</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>62537.4</v>
+      </c>
+      <c r="V11">
+        <v>0.8793507101607617</v>
+      </c>
+      <c r="W11">
+        <v>0.1432379273023912</v>
+      </c>
+      <c r="X11">
+        <v>0.1738917187747792</v>
+      </c>
+      <c r="Y11">
+        <v>-0.03065379147238803</v>
+      </c>
+      <c r="Z11">
+        <v>0.1218910951665832</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.08080472437316523</v>
+      </c>
+      <c r="AC11">
+        <v>-0.08080472437316523</v>
+      </c>
+      <c r="AD11">
+        <v>325580</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>325580</v>
+      </c>
+      <c r="AG11">
+        <v>263042.6</v>
+      </c>
+      <c r="AH11">
+        <v>0.8207257062493682</v>
+      </c>
+      <c r="AI11">
+        <v>0.8128053668421445</v>
+      </c>
+      <c r="AJ11">
+        <v>0.7871748977960578</v>
+      </c>
+      <c r="AK11">
+        <v>0.7781729151523596</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Banca Popolare di Sondrio S.p.A (BIT:BPSO)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.14</v>
+      </c>
+      <c r="E12">
+        <v>0.285</v>
+      </c>
+      <c r="F12">
+        <v>-0.0583</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>607.3</v>
+      </c>
+      <c r="L12">
+        <v>0.3921859864384888</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>2473.1</v>
+      </c>
+      <c r="V12">
+        <v>0.6524469067405355</v>
+      </c>
+      <c r="W12">
+        <v>0.1569980869655137</v>
+      </c>
+      <c r="X12">
+        <v>0.1429797671068867</v>
+      </c>
+      <c r="Y12">
+        <v>0.01401831985862698</v>
+      </c>
+      <c r="Z12">
+        <v>0.1046658600715121</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.08147985671050051</v>
+      </c>
+      <c r="AC12">
+        <v>-0.08147985671050051</v>
+      </c>
+      <c r="AD12">
+        <v>11961.7</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>11961.7</v>
+      </c>
+      <c r="AG12">
+        <v>9488.6</v>
+      </c>
+      <c r="AH12">
+        <v>0.7593669455695078</v>
+      </c>
+      <c r="AI12">
+        <v>0.727615027129614</v>
+      </c>
+      <c r="AJ12">
+        <v>0.714551437973959</v>
+      </c>
+      <c r="AK12">
+        <v>0.6793828088640677</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>BPER Banca SpA (BIT:BPE)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D13">
         <v>0.26</v>
       </c>
-      <c r="E9">
+      <c r="E13">
         <v>0.226</v>
       </c>
-      <c r="F9">
+      <c r="F13">
         <v>0.0833</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>1750.5</v>
       </c>
-      <c r="L9">
+      <c r="L13">
         <v>0.3030696514828858</v>
       </c>
-      <c r="M9">
+      <c r="M13">
         <v>475.5325</v>
       </c>
-      <c r="N9">
+      <c r="N13">
         <v>0.05274961452706076</v>
       </c>
-      <c r="O9">
+      <c r="O13">
         <v>0.2716552413596116</v>
       </c>
-      <c r="P9">
+      <c r="P13">
         <v>475.5325</v>
       </c>
-      <c r="Q9">
+      <c r="Q13">
         <v>0.05274961452706076</v>
       </c>
-      <c r="R9">
+      <c r="R13">
         <v>0.2716552413596116</v>
       </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>9940.1</v>
       </c>
-      <c r="V9">
+      <c r="V13">
         <v>1.102630090184029</v>
       </c>
-      <c r="W9">
+      <c r="W13">
         <v>0.1865846639237673</v>
       </c>
-      <c r="X9">
-        <v>0.1453162382371421</v>
-      </c>
-      <c r="Y9">
-        <v>0.04126842568662523</v>
-      </c>
-      <c r="Z9">
+      <c r="X13">
+        <v>0.1452975990877391</v>
+      </c>
+      <c r="Y13">
+        <v>0.04128706483602823</v>
+      </c>
+      <c r="Z13">
         <v>0.1990783505438904</v>
       </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.08154039462781529</v>
-      </c>
-      <c r="AC9">
-        <v>-0.08154039462781529</v>
-      </c>
-      <c r="AD9">
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.08153602165761767</v>
+      </c>
+      <c r="AC13">
+        <v>-0.08153602165761767</v>
+      </c>
+      <c r="AD13">
         <v>29409.8</v>
       </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
         <v>29409.8</v>
       </c>
-      <c r="AG9">
+      <c r="AG13">
         <v>19469.7</v>
       </c>
-      <c r="AH9">
+      <c r="AH13">
         <v>0.7653878885196241</v>
       </c>
-      <c r="AI9">
+      <c r="AI13">
         <v>0.7094083479670403</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ13">
         <v>0.6835167072734039</v>
       </c>
-      <c r="AK9">
+      <c r="AK13">
         <v>0.6177582043805347</v>
       </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
         <v>0</v>
       </c>
     </row>
